--- a/artfynd/A 38646-2023 artfynd.xlsx
+++ b/artfynd/A 38646-2023 artfynd.xlsx
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119819434</v>
+        <v>119819433</v>
       </c>
       <c r="B3" t="n">
-        <v>91832</v>
+        <v>91840</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,25 +798,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>693162</v>
+        <v>693159</v>
       </c>
       <c r="R3" t="n">
-        <v>7231118</v>
+        <v>7231125</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119819430</v>
+        <v>119819434</v>
       </c>
       <c r="B4" t="n">
-        <v>91852</v>
+        <v>91832</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,25 +909,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4366</v>
+        <v>4361</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -941,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>693149</v>
+        <v>693162</v>
       </c>
       <c r="R4" t="n">
-        <v>7231154</v>
+        <v>7231118</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119819433</v>
+        <v>119819430</v>
       </c>
       <c r="B5" t="n">
-        <v>91840</v>
+        <v>91852</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1024,21 +1024,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>4366</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1052,10 +1052,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>693159</v>
+        <v>693149</v>
       </c>
       <c r="R5" t="n">
-        <v>7231125</v>
+        <v>7231154</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 38646-2023 artfynd.xlsx
+++ b/artfynd/A 38646-2023 artfynd.xlsx
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119819433</v>
+        <v>119819430</v>
       </c>
       <c r="B3" t="n">
-        <v>91840</v>
+        <v>91852</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,21 +802,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>4366</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>693159</v>
+        <v>693149</v>
       </c>
       <c r="R3" t="n">
-        <v>7231125</v>
+        <v>7231154</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119819434</v>
+        <v>119819433</v>
       </c>
       <c r="B4" t="n">
-        <v>91832</v>
+        <v>91840</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,25 +909,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -941,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>693162</v>
+        <v>693159</v>
       </c>
       <c r="R4" t="n">
-        <v>7231118</v>
+        <v>7231125</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119819430</v>
+        <v>119819429</v>
       </c>
       <c r="B5" t="n">
-        <v>91852</v>
+        <v>91834</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1020,25 +1020,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4366</v>
+        <v>4362</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1052,10 +1052,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>693149</v>
+        <v>693114</v>
       </c>
       <c r="R5" t="n">
-        <v>7231154</v>
+        <v>7231203</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1119,10 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119819429</v>
+        <v>119819434</v>
       </c>
       <c r="B6" t="n">
-        <v>91834</v>
+        <v>91832</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1135,21 +1135,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4362</v>
+        <v>4361</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>693114</v>
+        <v>693162</v>
       </c>
       <c r="R6" t="n">
-        <v>7231203</v>
+        <v>7231118</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 38646-2023 artfynd.xlsx
+++ b/artfynd/A 38646-2023 artfynd.xlsx
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119819430</v>
+        <v>119819429</v>
       </c>
       <c r="B3" t="n">
-        <v>91852</v>
+        <v>91834</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,25 +798,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4366</v>
+        <v>4362</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>693149</v>
+        <v>693114</v>
       </c>
       <c r="R3" t="n">
-        <v>7231154</v>
+        <v>7231203</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119819429</v>
+        <v>119819434</v>
       </c>
       <c r="B5" t="n">
-        <v>91834</v>
+        <v>91832</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1024,21 +1024,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4362</v>
+        <v>4361</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1052,10 +1052,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>693114</v>
+        <v>693162</v>
       </c>
       <c r="R5" t="n">
-        <v>7231203</v>
+        <v>7231118</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1119,10 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119819434</v>
+        <v>119819430</v>
       </c>
       <c r="B6" t="n">
-        <v>91832</v>
+        <v>91852</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1131,25 +1131,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4361</v>
+        <v>4366</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>693162</v>
+        <v>693149</v>
       </c>
       <c r="R6" t="n">
-        <v>7231118</v>
+        <v>7231154</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 38646-2023 artfynd.xlsx
+++ b/artfynd/A 38646-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>119819432</v>
       </c>
       <c r="B2" t="n">
-        <v>78262</v>
+        <v>78278</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119819429</v>
+        <v>119819434</v>
       </c>
       <c r="B3" t="n">
-        <v>91834</v>
+        <v>91850</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,21 +802,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4362</v>
+        <v>4361</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>693114</v>
+        <v>693162</v>
       </c>
       <c r="R3" t="n">
-        <v>7231203</v>
+        <v>7231118</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -900,7 +900,7 @@
         <v>119819433</v>
       </c>
       <c r="B4" t="n">
-        <v>91840</v>
+        <v>91858</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119819434</v>
+        <v>119819430</v>
       </c>
       <c r="B5" t="n">
-        <v>91832</v>
+        <v>91870</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1020,25 +1020,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4361</v>
+        <v>4366</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1052,10 +1052,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>693162</v>
+        <v>693149</v>
       </c>
       <c r="R5" t="n">
-        <v>7231118</v>
+        <v>7231154</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1119,7 +1119,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119819430</v>
+        <v>119819429</v>
       </c>
       <c r="B6" t="n">
         <v>91852</v>
@@ -1131,25 +1131,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4366</v>
+        <v>4362</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>693149</v>
+        <v>693114</v>
       </c>
       <c r="R6" t="n">
-        <v>7231154</v>
+        <v>7231203</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 38646-2023 artfynd.xlsx
+++ b/artfynd/A 38646-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119819432</v>
+        <v>119819429</v>
       </c>
       <c r="B2" t="n">
-        <v>78278</v>
+        <v>91852</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6446</v>
+        <v>4362</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>693153</v>
+        <v>693114</v>
       </c>
       <c r="R2" t="n">
-        <v>7231142</v>
+        <v>7231203</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119819434</v>
+        <v>119819432</v>
       </c>
       <c r="B3" t="n">
-        <v>91850</v>
+        <v>78278</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,21 +802,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4361</v>
+        <v>6446</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>693162</v>
+        <v>693153</v>
       </c>
       <c r="R3" t="n">
-        <v>7231118</v>
+        <v>7231142</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119819433</v>
+        <v>119819434</v>
       </c>
       <c r="B4" t="n">
-        <v>91858</v>
+        <v>91850</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,25 +909,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -941,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>693159</v>
+        <v>693162</v>
       </c>
       <c r="R4" t="n">
-        <v>7231125</v>
+        <v>7231118</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1119,10 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119819429</v>
+        <v>119819433</v>
       </c>
       <c r="B6" t="n">
-        <v>91852</v>
+        <v>91858</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1131,25 +1131,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>693114</v>
+        <v>693159</v>
       </c>
       <c r="R6" t="n">
-        <v>7231203</v>
+        <v>7231125</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 38646-2023 artfynd.xlsx
+++ b/artfynd/A 38646-2023 artfynd.xlsx
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119819432</v>
+        <v>119819434</v>
       </c>
       <c r="B3" t="n">
-        <v>78278</v>
+        <v>91850</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,21 +802,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>4361</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>693153</v>
+        <v>693162</v>
       </c>
       <c r="R3" t="n">
-        <v>7231142</v>
+        <v>7231118</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119819434</v>
+        <v>119819433</v>
       </c>
       <c r="B4" t="n">
-        <v>91850</v>
+        <v>91858</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,25 +909,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -941,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>693162</v>
+        <v>693159</v>
       </c>
       <c r="R4" t="n">
-        <v>7231118</v>
+        <v>7231125</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119819430</v>
+        <v>119819432</v>
       </c>
       <c r="B5" t="n">
-        <v>91870</v>
+        <v>78278</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1020,25 +1020,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4366</v>
+        <v>6446</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1052,10 +1052,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>693149</v>
+        <v>693153</v>
       </c>
       <c r="R5" t="n">
-        <v>7231154</v>
+        <v>7231142</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1119,10 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119819433</v>
+        <v>119819430</v>
       </c>
       <c r="B6" t="n">
-        <v>91858</v>
+        <v>91870</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1135,21 +1135,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>4366</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>693159</v>
+        <v>693149</v>
       </c>
       <c r="R6" t="n">
-        <v>7231125</v>
+        <v>7231154</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
